--- a/business_forms/015_retrospective_survey--business_forms.xlsx
+++ b/business_forms/015_retrospective_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is this survey used for</t>
+          <t>What is the primary purpose of this survey?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are the goals of the business</t>
+          <t>What are the goals of the business?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>goals_page</t>
+          <t>metrics_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_are_the_goals</t>
+          <t>What metrics are being tracked?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>metrics_page</t>
+          <t>target_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What metrics are being tracked</t>
+          <t>What are the targets?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>metrics_page</t>
+          <t>score_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_metrics_are_being_tracked</t>
+          <t>What is the score?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>target_page</t>
+          <t>time_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What are the targets</t>
+          <t>When is this score valid?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>target_page</t>
+          <t>comments_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_are_the_targets</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>score_page</t>
+          <t>email_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the score</t>
+          <t>E-Mail Address</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>score_page</t>
+          <t>challenges_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_the_score</t>
+          <t>What are the key challenges the business is facing?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>score_page</t>
+          <t>opportunities_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_is_the_score_2</t>
+          <t>What are the key opportunities the business is facing?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_page</t>
+          <t>strengths_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>When is this score valid</t>
+          <t>What are the key strengths the business is facing?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time_page</t>
+          <t>weaknesses_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>when_is_this_score_valid</t>
+          <t>What are the key weaknesses the business is facing?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note_page</t>
+          <t>comments_page_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Additional Comments (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>note_page</t>
+          <t>submit_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email_page</t>
+          <t>submit_page_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E-Mail Address</t>
+          <t>Submit (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email_page</t>
+          <t>submit_page_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>e_mail_address</t>
+          <t>Submit (3)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email_page</t>
+          <t>submit_page_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Submit (4)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_page</t>
+          <t>submit_page_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>e_mail</t>
+          <t>Submit (5)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>note_page</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>email_page</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments (2)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email_page</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_page</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +940,9 @@
   <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>goal1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>goal1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>goal2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>goal2</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1004,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>goal1</t>
+          <t>goal3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>goal1</t>
+          <t>goal3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>goals_page_choices</t>
+          <t>metrics_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goal2</t>
+          <t>metric1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>goal2</t>
+          <t>metric1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>goals_page_choices</t>
+          <t>metrics_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>goal3</t>
+          <t>metric2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goal3</t>
+          <t>metric2</t>
         </is>
       </c>
     </row>
@@ -1216,454 +1055,454 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>metric3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>metric3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>metrics_page_choices</t>
+          <t>target_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>target1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>target1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>metrics_page_choices</t>
+          <t>target_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>target2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>target2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>metrics_page_choices</t>
+          <t>target_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>metric1</t>
+          <t>target3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>metric1</t>
+          <t>target3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>metrics_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>metric2</t>
+          <t>challenge1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>metric2</t>
+          <t>challenge1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>metrics_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>metric3</t>
+          <t>challenge2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>metric3</t>
+          <t>challenge2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>challenge3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>challenge3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>opportunities_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>opportunity1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>opportunity1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>opportunities_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>opportunity2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>opportunity2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>opportunities_page_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>target1</t>
+          <t>opportunity3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>target1</t>
+          <t>opportunity3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>strengths_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>target2</t>
+          <t>strength1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>target2</t>
+          <t>strength1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>target_page_choices</t>
+          <t>strengths_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>target3</t>
+          <t>strength2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>target3</t>
+          <t>strength2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note_page_choices</t>
+          <t>strengths_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>strength3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>strength3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note_page_choices</t>
+          <t>weaknesses_page_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weakness1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>weakness1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note_page_choices</t>
+          <t>weaknesses_page_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>weakness2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>weakness2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>email_page_choices</t>
+          <t>weaknesses_page_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>weakness3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>weakness3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>email_page_choices</t>
+          <t>submit_page_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>email_page_choices</t>
+          <t>submit_page_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_3_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>submit_page_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>submit_page_choices</t>
+          <t>submit_page_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>submit_page_choices</t>
+          <t>submit_page_5_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>submit_page_choices</t>
+          <t>submit_page_5_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
